--- a/光伏配储项目/电价数据/2026/三水站.xlsx
+++ b/光伏配储项目/电价数据/2026/三水站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51178</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.75895</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57489</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.60004</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.51822</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.5167200000000001</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43767</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45452</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44539</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42384</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.4231</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40908</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.4015</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.4025899999999999</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39151</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41698</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3922</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42079</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41394</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42394</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41342</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44462</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.36931</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29502</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.12869</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.10467</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.11917</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.10873</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.13144</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.04923</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.10851</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.15835</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.1942</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.25515</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09134</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.10148</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.04417</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15261</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21679</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25541</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24029</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.17094</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.4958399999999999</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14329</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.38307</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.28388</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.41438</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.3761</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.21328</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.64437</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5598200000000001</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.5682999999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.33991</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.61837</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.46202</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44682</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.45945</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.57838</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.47532</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.63678</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.82223</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.64025</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.6532</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.79702</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.16102</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.42977</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.68667</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.60077</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.8267599999999999</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.66416</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.6792</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.65207</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.4778</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.4812</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39778</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41639</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.4261</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7085499999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8028</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.55024</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.86458</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53634</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5180900000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50502</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50905</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48736</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46938</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37456</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41837</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.49795</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59993</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7515499999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.4284</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.38499</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.4413</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.43288</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.52207</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.17215</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29713</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.40212</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.50369</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.76781</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.17901</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.38192</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.38744</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.42028</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.7992400000000001</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.53949</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.13286</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28344</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.38805</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.5155599999999999</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.26681</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.38736</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.05778</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.35694</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.21581</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.43351</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.64232</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.78771</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.62463</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.18975</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.79008</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7402300000000001</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.66822</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.60589</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.77479</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.57172</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.45615</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.07961</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.39414</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.47104</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.67487</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44355</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43698</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.42156</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33468</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5174800000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.38451</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.52646</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.41934</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38213</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40435</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.41542</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.3889</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36753</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43711</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45372</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3717200000000001</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35609</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47377</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45362</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44788</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40076</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37119</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.46567</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.37799</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.48329</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.27086</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.30564</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.47661</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.40758</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.50988</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.48709</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.42412</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29394</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.16475</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.28007</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.28294</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29883</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27845</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.39855</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.40234</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.51523</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.43015</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.15545</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.51871</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.57165</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.86425</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.39232</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.40091</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.56486</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.64063</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.71499</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.5769500000000001</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.49843</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.44413</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5284</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.42553</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.48493</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.45204</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.47367</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.45943</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.41775</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.38989</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.44145</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.41885</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.40577</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.41052</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36905</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34232</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.43453</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36429</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46069</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30427</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38929</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.29216</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.36848</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.28176</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.29681</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.18177</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.44777</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.36817</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.09878000000000001</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.09851</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.17467</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28301</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.18002</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.22118</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.51418</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.06781999999999999</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.12112</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.23007</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.24395</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.28571</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.21705</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.23672</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.20066</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.26512</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.12459</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.1316</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.26889</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.29819</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30847</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.39077</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.44381</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.67065</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.47214</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.42797</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30219</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29625</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31205</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30263</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29926</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38189</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30058</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30515</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28922</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30551</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.2891</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29331</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.28966</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.28966</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.28957</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29793</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29172</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27837</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.25905</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04818</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.03912</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04906</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.05022</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04452</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04098</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04574</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04257</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03617</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04714</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04618999999999999</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04951</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04745000000000001</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04625</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04658</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04893</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04464</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04704999999999999</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04374</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04201</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04481</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04565</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21831</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.03954</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04541</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05512</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04972</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04784</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.01361</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.15582</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.0559</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.11332</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29025</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29368</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38794</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39237</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.3878</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37755</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39995</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41099</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46731</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.3962</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39972</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41642</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35061</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.67747</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39948</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44475</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42205</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.4219</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10256</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04372</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04542</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.0462</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0462</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.0462</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04397</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04665999999999999</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.09811</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00458</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04519</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04391</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04578</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04564</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04365</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04553</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04345</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04692</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04498</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04364</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04934</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04462</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04991</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04953</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04732</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04774</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19998</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14286</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29487</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29313</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29366</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29701</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29091</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29511</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26892</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29397</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29821</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30866</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30223</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33538</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31748</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40425</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31472</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28122</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.2908</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28808</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28094</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27124</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27101</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28113</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17243</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15867</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17096</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14773</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15946</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15862</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23618</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21403</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22658</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26881</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28577</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29084</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29081</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28094</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.2805299999999999</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27176</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32248</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30504</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30957</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.2982</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38385</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.4287</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45692</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41884</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41572</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38901</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40276</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29946</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15634</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29557</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31384</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30078</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50773</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7909400000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220800000000001</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49804</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78108</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92052</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49465</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91531</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86546</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29803</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.89052</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63225</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19009</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87024</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5394500000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33387</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03502</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5337499999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79344</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.52938</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77546</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7795</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8770800000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87515</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49546</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40094</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40291</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4526</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21002</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5511200000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62485</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5390900000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49859</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45624</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42466</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.4377200000000001</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45012</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38897</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45278</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42001</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39997</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38579</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41458</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43352</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39018</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40291</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45077</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5854299999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42694</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59561</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60151</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66186</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47383</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41909</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58233</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45183</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.87836</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6284299999999999</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8756499999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.85822</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8652300000000001</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44312</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.46168</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.29455</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33653</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30309</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35421</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.40932</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41192</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45141</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41426</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37445</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35325</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91575</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46359</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.40302</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4092</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49875</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29112</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16654</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26262</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19898</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27713</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19091</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27823</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28923</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25567</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.27606</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27648</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33358</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43152</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42314</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44756</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.41978</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39969</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59458</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88978</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.32795</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13634</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69737</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.78739</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64295</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57657</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44835</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44967</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49964</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43924</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.4364</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41445</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41236</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42256</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.4987</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41237</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43346</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41184</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43346</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38996</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.4267</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44887</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39581</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42293</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43276</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41237</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41241</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39455</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40126</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49207</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29674</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.37003</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.37474</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.9792000000000001</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.61956</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.18025</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>1.14425</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25039</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.02128</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.69968</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.40578</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.68941</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.37553</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.37468</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.39473</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.40408</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.43356</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.42052</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40834</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39972</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38695</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>1.35139</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.40285</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57504</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46142</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.74407</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46337</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.4362799999999999</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.41924</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3233</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42092</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38898</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39733</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>1.32402</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.93484</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.16408</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.1687</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>1.09182</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.17559</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.9939</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.9817899999999999</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14999</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.15819</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.15018</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.1573</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28041</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.30281</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.28859</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.19981</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.2527</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.25293</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.1579</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.16308</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>1.31894</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38203</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44776</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39845</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.43941</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43777</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43712</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44312</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40154</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.3896</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39066</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34823</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5354</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38807</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46642</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42202</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41418</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36936</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37855</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39029</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36959</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29838</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29518</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28234</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27185</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26665</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20321</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.25016</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24365</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27033</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28837</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24229</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3146600000000001</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28591</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33697</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24438</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38079</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.3693</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37939</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.37983</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35965</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36557</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.4174</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39092</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41068</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.35355</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.37504</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.44026</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.53318</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.28463</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24937</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.47353</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.12212</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.27058</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.26402</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.30358</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.43051</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.36146</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.44324</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.42755</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7014400000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37157</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.31778</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.52816</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24806</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37899</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30676</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.29992</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30533</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28286</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.36629</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30145</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28638</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>1.31568</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34372</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.36746</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.36378</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37136</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.39621</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34939</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35708</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30707</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36861</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38227</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37851</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38431</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42449</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41122</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65584</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7680399999999999</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45162</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.2936</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45696</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39455</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34417</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41089</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37598</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37003</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37851</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.29392</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.25974</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28521</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28476</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.20059</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.26086</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28085</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28021</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.22034</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28603</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28017</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29391</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30655</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.21761</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29696</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.55011</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.53128</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.5158200000000001</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.43138</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.5440199999999999</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.52808</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36574</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.4367799999999999</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38568</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.42178</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6426000000000001</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.60738</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.59237</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46494</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.6670499999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.46943</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.82324</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.47228</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.71696</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40663</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37344</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47539</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42945</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41848</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37803</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36679</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35969</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48905</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.53685</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.48488</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.49218</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.4163</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39705</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40949</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40721</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41549</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39805</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39445</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.4097</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40757</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.3932</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38721</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41743</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38696</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38936</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39889</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39901</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41136</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39885</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44837</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44748</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.55706</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49794</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44874</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.6445700000000001</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.44989</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.46934</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.37333</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38522</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.4169</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44769</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.39726</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.43581</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.46075</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30245</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.4045299999999999</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.40239</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41663</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29057</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.38181</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.65178</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.37336</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.36979</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.29575</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38828</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.41814</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43981</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49257</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43907</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.5088199999999999</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.51169</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.54599</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.69813</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.72994</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.4808</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.6537500000000001</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.81047</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5909500000000001</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5260199999999999</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.83682</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7765599999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6275499999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6768</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44891</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.4782</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48327</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46959</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41695</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5557799999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42912</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44112</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45548</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43505</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42467</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44531</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41648</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45432</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39694</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40417</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39625</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38585</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3777</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37275</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37303</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36574</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37924</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39916</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38667</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39409</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.2078</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39227</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40337</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44986</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.4613</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11488</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18005</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29697</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29392</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37652</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37003</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41684</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43204</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39143</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41654</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38595</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38489</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39005</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40813</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37621</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37878</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.3988</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37431</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39402</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37917</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36458</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44371</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39637</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.3778</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27932</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22558</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28693</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23062</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28842</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.2502</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.26131</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.1391</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29471</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29827</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25094</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04294</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25052</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.17124</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18331</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.2799</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22981</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25077</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26656</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23358</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27616</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28416</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28473</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37531</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38232</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.34912</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1.32574</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1.337</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30433</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28737</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.2487</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.23384</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16106</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.1991</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.23806</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01828</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00103</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.1107</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.02044</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03899</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04903</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01167</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.03581</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03195</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04704999999999999</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04641</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02393</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02123</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04907</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.19986</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04903</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04906</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04882</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00057</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.0491</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04888</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04906</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03467</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04902</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04875</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04336</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.17832</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.18985</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2307</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28041</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.25948</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.26119</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.25696</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.26465</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.27867</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.29987</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.28679</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.2852</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.2789700000000001</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30676</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28365</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.28305</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29013</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41062</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30618</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.28761</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.28443</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.27952</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.27745</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.11605</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5555399999999999</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.13584</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.26891</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.24685</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.29236</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30198</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.28771</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.25923</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.23579</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.22372</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.25334</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.24327</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.20652</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.23164</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.23628</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.27251</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.25824</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.25696</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.23802</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29454</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.26394</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.29855</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.29578</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.2689</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.2707</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.2133</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.1331</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6207699999999999</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.59066</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.6349199999999999</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.57198</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>1.14956</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.30658</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>1.11938</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>1.23306</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>1.17422</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.09877</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.10934</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.05889</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.22369</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.09198999999999999</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.00408</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.02085</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.08220000000000001</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.16467</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02871</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.10074</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.11006</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.13121</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.02576</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.08231999999999999</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.09528</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.09387000000000001</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.13743</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>1.2592</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29627</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27994</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>1.33356</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>1.33337</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>1.32892</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.33887</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.35976</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.37557</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.33823</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.38861</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.37826</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.45305</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.37421</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.3753</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.36262</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.36363</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.35482</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.37005</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.35848</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.3679</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3228</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1.35449</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1.37132</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.39007</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="R138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.3062</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.55636</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.55169</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.41139</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.43141</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.38976</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.45091</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.36801</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.48341</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.39311</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.45014</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.38505</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.3787</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.36864</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.44762</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14253</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27923</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27025</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.27499</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31239</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32259</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36641</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.50575</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.4079700000000001</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32841</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36636</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.2766</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.30294</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36874</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.37489</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.37705</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.6416000000000001</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.60115</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.35228</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.5069399999999999</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36413</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35428</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.43593</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26354</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.28536</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28834</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41353</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40104</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.49393</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.50439</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.46761</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.48985</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.4247</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.5871900000000001</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.41764</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.38714</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.49007</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.38469</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.4151</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.37262</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36898</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45742</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40081</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38421</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40461</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.30764</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3723399999999999</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36817</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.48104</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40187</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40175</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39288</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38022</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37469</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37389</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37641</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36655</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34677</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39848</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3752799999999999</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36166</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.41448</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.4209</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.38987</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.37453</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.4643</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.40403</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.38111</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.29167</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.37233</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27722</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38623</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.3951</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.38668</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38881</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.3888</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.43051</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.39448</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41733</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.40234</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.43712</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51444</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.58466</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38153</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.41175</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.52032</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.50942</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5500499999999999</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.46718</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.51312</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.40468</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.8919199999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.59001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5883700000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39797</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44362</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39885</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37453</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37691</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37281</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.25441</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30363</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29846</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.29448</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.22106</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.17201</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.29079</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.15511</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.07337</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.41806</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.21462</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.04289</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.21315</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.17065</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.01131</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26531</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.16749</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.06359000000000001</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.06148</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.07933</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.17011</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08518000000000001</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.06157</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.17653</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.28621</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.36898</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.38247</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36392</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.38789</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.24306</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.30693</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.37812</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42549</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.37846</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.40213</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41202</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38538</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42712</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38907</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38591</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.42064</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.3737799999999999</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.43467</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35725</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.46763</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.41975</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.39426</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38674</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37174</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34677</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36313</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37036</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38442</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38595</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30141</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.30721</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.2542</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.24872</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.27146</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.2444</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11365</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.1119</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.11984</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.16716</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.20031</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.40176</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.20059</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00363</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01949</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04915</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.02682</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.11454</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.24211</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04903</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.23637</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.1944</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.28568</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.50038</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.39488</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.38968</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37303</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36478</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39895</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.58636</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37268</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36931</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.36352</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36698</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37137</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.41336</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.39673</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.36986</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38638</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35836</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.6214299999999999</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.36931</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.45669</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37109</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.27879</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.25604</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.22852</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14299</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.20386</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.22741</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.22876</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11327</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.14876</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.00189</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04728</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.0474</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04675</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04755</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04736</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04186</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.07798999999999999</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03034</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06277000000000001</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09611</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.16853</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.19379</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.1194</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.25143</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.2272</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12302</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26095</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.1447</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.1165</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.23516</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.18304</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.23347</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.24069</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.2014</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.24176</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.27135</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.2731</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.30279</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.30532</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38984</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.46771</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38495</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.38316</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.3883</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37577</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38131</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36455</v>
       </c>
     </row>
   </sheetData>
